--- a/test_iiko_export.xlsx
+++ b/test_iiko_export.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="42">
   <si>
     <t>skuId</t>
   </si>
@@ -38,10 +38,10 @@
     <t>asOf</t>
   </si>
   <si>
-    <t>MEAT_001</t>
-  </si>
-  <si>
-    <t>Говядина лопатка</t>
+    <t>MEAT_BEEF_BONE_001</t>
+  </si>
+  <si>
+    <t>Говядина на косточке</t>
   </si>
   <si>
     <t>kg</t>
@@ -50,43 +50,61 @@
     <t>2025-01-17</t>
   </si>
   <si>
-    <t>BEET_001</t>
-  </si>
-  <si>
-    <t>Свёкла столовая</t>
-  </si>
-  <si>
-    <t>AUTO_МОРКОВЬ</t>
-  </si>
-  <si>
-    <t>МОРКОВЬ</t>
+    <t>VEG_BEETROOT_001</t>
+  </si>
+  <si>
+    <t>Свекла</t>
+  </si>
+  <si>
+    <t>VEG_CABBAGE_001</t>
+  </si>
+  <si>
+    <t>Капуста белокочанная</t>
+  </si>
+  <si>
+    <t>VEG_CARROT_001</t>
   </si>
   <si>
     <t>Морковь</t>
   </si>
   <si>
-    <t>ONION_001</t>
+    <t>VEG_ONION_001</t>
   </si>
   <si>
     <t>Лук репчатый</t>
   </si>
   <si>
-    <t>OIL_001</t>
-  </si>
-  <si>
-    <t>Масло растительное</t>
+    <t>VEG_POTATO_001</t>
+  </si>
+  <si>
+    <t>Картофель</t>
+  </si>
+  <si>
+    <t>SAUCE_TOMATO_001</t>
+  </si>
+  <si>
+    <t>Томатная паста</t>
+  </si>
+  <si>
+    <t>OIL_SUNFLOWER_001</t>
+  </si>
+  <si>
+    <t>Растительное масло</t>
   </si>
   <si>
     <t>l</t>
   </si>
   <si>
-    <t>EGG_001</t>
-  </si>
-  <si>
-    <t>Яйца куриные</t>
-  </si>
-  <si>
-    <t>pcs</t>
+    <t>SPICE_SALT_001</t>
+  </si>
+  <si>
+    <t>Соль поваренная</t>
+  </si>
+  <si>
+    <t>SPICE_BAY_001</t>
+  </si>
+  <si>
+    <t>Лавровый лист</t>
   </si>
   <si>
     <t>dishCode</t>
@@ -454,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="15.7109375" customWidth="1"/>
@@ -528,10 +546,10 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
@@ -545,13 +563,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
         <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>
@@ -565,16 +583,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>20</v>
@@ -585,21 +603,101 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7">
+        <v>20</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
         <v>23</v>
       </c>
-      <c r="F7">
-        <v>20</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10">
+        <v>20</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
         <v>10</v>
       </c>
     </row>
@@ -610,7 +708,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="15.7109375" customWidth="1"/>
@@ -618,42 +716,42 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D2">
         <v>300</v>
@@ -668,7 +766,7 @@
         <v>8</v>
       </c>
       <c r="H2">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="I2" t="s">
         <v>9</v>
@@ -676,13 +774,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D3">
         <v>300</v>
@@ -697,7 +795,7 @@
         <v>12</v>
       </c>
       <c r="H3">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="I3" t="s">
         <v>9</v>
@@ -705,13 +803,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D4">
         <v>300</v>
@@ -719,11 +817,14 @@
       <c r="E4">
         <v>1800</v>
       </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="I4" t="s">
         <v>9</v>
@@ -731,13 +832,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D5">
         <v>300</v>
@@ -746,13 +847,13 @@
         <v>1800</v>
       </c>
       <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
       <c r="H5">
-        <v>0.135</v>
+        <v>0.17</v>
       </c>
       <c r="I5" t="s">
         <v>9</v>
@@ -760,13 +861,13 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D6">
         <v>300</v>
@@ -775,27 +876,27 @@
         <v>1800</v>
       </c>
       <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
         <v>18</v>
       </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
       <c r="H6">
-        <v>0.05</v>
+        <v>0.135</v>
       </c>
       <c r="I6" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D7">
         <v>300</v>
@@ -804,16 +905,132 @@
         <v>1800</v>
       </c>
       <c r="F7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>0.32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>300</v>
+      </c>
+      <c r="E8">
+        <v>1800</v>
+      </c>
+      <c r="F8" t="s">
         <v>21</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G8" t="s">
         <v>22</v>
       </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="H8">
+        <v>0.03</v>
+      </c>
+      <c r="I8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9">
+        <v>300</v>
+      </c>
+      <c r="E9">
+        <v>1800</v>
+      </c>
+      <c r="F9" t="s">
         <v>23</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9">
+        <v>0.04</v>
+      </c>
+      <c r="I9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10">
+        <v>300</v>
+      </c>
+      <c r="E10">
+        <v>1800</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10">
+        <v>0.015</v>
+      </c>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11">
+        <v>300</v>
+      </c>
+      <c r="E11">
+        <v>1800</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11">
+        <v>0.002</v>
+      </c>
+      <c r="I11" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
